--- a/光伏配储项目/电价数据/2026/蝶岭站.xlsx
+++ b/光伏配储项目/电价数据/2026/蝶岭站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7136399999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56571</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.52279</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.46042</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45459</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.22587</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26573</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.08228000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06787</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05898</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03970000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.06171</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.02136</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.00962</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01823</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.005059999999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14486</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18644</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.12881</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00613</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.009679999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11948</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.18367</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2288</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.13011</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.20387</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.04702000000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.11839</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.53147</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7484700000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61198</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.52762</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.54242</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.10963</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.59296</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5466599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.51047</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.60603</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.56674</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48042</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42311</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6340800000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43821</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74654</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.04221</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7985399999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53654</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5239299999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50662</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50208</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47424</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5164099999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62867</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.71912</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45739</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.03001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.62285</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5987899999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.005059999999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27339</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.24814</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.18496</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25413</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23319</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25132</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.48592</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6881499999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7926799999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78706</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.7915</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5890700000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3337</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46447</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43224</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44829</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47398</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44236</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.28136</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.14804</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.25487</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.25903</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.08368</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.22251</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.20908</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2799700000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25204</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.23382</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.06297999999999999</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.49342</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.07728</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5143099999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34338</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.22683</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14185</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.13867</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.10132</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26817</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22656</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.14048</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28805</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.46506</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.02683</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.03215999999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06628000000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.21793</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.06644</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.09767000000000001</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.12874</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25477</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19594</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18331</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23324</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16266</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23759</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25316</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48535</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29093</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28447</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04534000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03990999999999999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03977</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04461</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04168</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04449</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04552</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04443</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0458</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04492</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04557</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04704</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04697</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22034</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05142</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05356</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14644</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03685</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3514</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66354</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04245</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04582</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04458</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04261</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03193</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.0414</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10652</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03767</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04215</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04225</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04214</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04432</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04432</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04154</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04135</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03986</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04496</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04404</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04433</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04189</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04052</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04379</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04686</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04677000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20143</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14402</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27041</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33696</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3207</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27265</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17358</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15983</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1489</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16063</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15993</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23833</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21534</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22789</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42164</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9229299999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.89179</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31092</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.91475</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63605</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2138</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88185</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56502</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35833</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05173</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55844</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81456</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7966599999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79634</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8796799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88625</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5152899999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42834</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47523</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23544</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8796499999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55152</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65004</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54535</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45926</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44212</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45112</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5886399999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59661</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60154</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65646</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45147</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44634</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86181</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.64707</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.82885</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8117799999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84964</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98522</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48681</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54101</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.60876</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.45635</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41113</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16455</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20051</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25466</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27037</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43212</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27895</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3502</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14066</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70711</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7998099999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6523600000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58749</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.53977</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.05697</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6118899999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.64689</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21791</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.5257500000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26551</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58533</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7169800000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46577</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32565</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23578</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14487</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14718</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15403</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14436</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14072</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14412</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14256</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14465</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26664</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14208</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03341</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11412</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11324</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14527</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14144</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14661</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44117</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44102</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44535</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35005</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5477000000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46972</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27864</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.24503</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18533</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24169</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22484</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22488</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26688</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24351</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44227</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36054</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03636</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25011</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18207</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27048</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25219</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.73397</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30099</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34941</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.59829</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43363</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.66937</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.86938</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34507</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13476</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19499</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24575</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02242</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11153</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02212</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23083</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24053</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14448</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.21045</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21751</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.67535</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6363300000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.63228</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.47682</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.65815</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48747</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.84861</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45721</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48802</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49914</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.48438</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47701</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4648</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45565</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.57324</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50907</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42633</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00286</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.00671</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6544800000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.12644</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08835999999999999</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.0328</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26295</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.00168</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51739</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5193</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.59965</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7311599999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.74183</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7106399999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5684400000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.53349</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.85897</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7892</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62818</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.68169</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.45893</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.49116</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48656</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48011</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55398</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.44186</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43049</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42135</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46411</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15703</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45331</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46398</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18325</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36409</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23438</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24767</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1339</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01133</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16011</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00371</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14529</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15372</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.03075</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.03928</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2185</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23159</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21834</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26691</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35228</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22781</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21785</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15163</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.1808</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00138</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04223</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.06864000000000001</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03275</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04136</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03129</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04805</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.17046</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21546</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24546</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24652</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25763</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27428</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25601</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25197</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23579</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.18057</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05847</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06792000000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25158</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22705</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14766</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26237</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24451</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22343</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20747</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.19092</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21484</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22702</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.1916</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22396</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22119</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24519</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23349</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24751</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.25058</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18543</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06756999999999999</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49513</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.55464</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.08244</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.23385</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.01494</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20384</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09570000000000001</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04535</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05884</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00389</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20885</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03493</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02928</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13219</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03813</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.03962</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.08492</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02883</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.03204</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.24058</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3253</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11463</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.43335</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.16969</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.25997</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11638</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26978</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16764</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.15149</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07428</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33119</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.51897</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5088199999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.19487</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26289</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26061</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24278</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26735</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42684</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49299</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.47227</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48153</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.12906</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47646</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.73797</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.22349</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.16383</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.24433</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17641</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.44172</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46893</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5639400000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56024</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45991</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54847</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46819</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5393600000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5316900000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.73217</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77522</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55208</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55423</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44387</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37565</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26118</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.26247</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21166</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23605</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.17795</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.02432</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14449</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.16962</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.02609</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.00899</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.04844</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02278</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23466</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.03979</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03401</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02747</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03364</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.03292</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12403</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.08567</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.13541</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.17376</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.20983</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.25395</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19277</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.16674</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22663</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42131</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37853</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.81809</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.22637</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.23099</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24648</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.09281</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03305</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.12557</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03341</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00766</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01034</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15396</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.18663</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03858</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.18472</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13803</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.16386</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.19229</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.22965</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.20653</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.23142</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.25177</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.47188</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.51627</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38563</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5248700000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21881</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19956</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12681</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17659</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20006</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12516</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.06256</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07806999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04579</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04585</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04577000000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04285</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06951</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02816</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05859</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08258</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.14107</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.15495</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10208</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.21037</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18315</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10377</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04704999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23813</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10074</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20887</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.19763</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2019</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21223</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23888</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25665</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42231</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4967200000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42884</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38421</v>
       </c>
     </row>
   </sheetData>
